--- a/04_input_files/crabbing_holidays.xlsx
+++ b/04_input_files/crabbing_holidays.xlsx
@@ -1,105 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattg\Desktop\github\FWC-estimation-method\04_input_files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829BE5FF-3140-4A35-8125-5EA42BE8B07C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
-  <si>
-    <t>season</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>holiday_name</t>
-  </si>
-  <si>
-    <t>2024-25</t>
-  </si>
-  <si>
-    <t>2024-11-29</t>
-  </si>
-  <si>
-    <t>Native American Heritage Day</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>New Year's Eve</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>New Year's Day</t>
-  </si>
-  <si>
-    <t>2025-02-08</t>
-  </si>
-  <si>
-    <t>Super Bowl Eve</t>
-  </si>
-  <si>
-    <t>2025-05-24</t>
-  </si>
-  <si>
-    <t>Memorial Day weekend - Saturday</t>
-  </si>
-  <si>
-    <t>2025-05-25</t>
-  </si>
-  <si>
-    <t>Memorial Day weekend - Sunday</t>
-  </si>
-  <si>
-    <t>2025-05-26</t>
-  </si>
-  <si>
-    <t>Memorial Day</t>
-  </si>
-  <si>
-    <t>2025-06-15</t>
-  </si>
-  <si>
-    <t>Father's Day</t>
-  </si>
-  <si>
-    <t>2025-07-04</t>
-  </si>
-  <si>
-    <t>Independence Day</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>Labor Day</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -129,21 +54,15 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -431,137 +350,1052 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>holiday_name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-11-25</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-02-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023-06-18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2022-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-05-26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-05-27</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2023-24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Independence Day (observed)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>federal observed day</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2027-05-29</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2027-05-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2027-05-31</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2027-07-04</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Independence Day (observed)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>federal observed day</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2027-09-06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/04_input_files/crabbing_holidays.xlsx
+++ b/04_input_files/crabbing_holidays.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,17 +384,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2022-11-25</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Native American Heritage Day</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Friday after Thanksgiving</t>
+          <t>Veterans Day</t>
         </is>
       </c>
     </row>
@@ -406,12 +401,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2022-12-31</t>
+          <t>2022-11-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>Thanksgiving Day</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4th Thursday of November</t>
         </is>
       </c>
     </row>
@@ -423,12 +423,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-11-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New Year's Day</t>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
         </is>
       </c>
     </row>
@@ -440,17 +445,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2022-12-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Super Bowl Eve</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Saturday; no-op for day typing</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
@@ -462,17 +462,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Saturday</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>no-op for day typing</t>
+          <t>New Year's Day</t>
         </is>
       </c>
     </row>
@@ -484,17 +479,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Sunday</t>
+          <t>Super Bowl Eve</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>no-op for day typing</t>
+          <t>Saturday; no-op for day typing</t>
         </is>
       </c>
     </row>
@@ -506,12 +501,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memorial Day</t>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
@@ -523,17 +523,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Father's Day</t>
+          <t>Memorial Day weekend - Sunday</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sunday; no-op for day typing</t>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Independence Day</t>
+          <t>Memorial Day</t>
         </is>
       </c>
     </row>
@@ -562,68 +562,68 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Labor Day</t>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2023-24</t>
+          <t>2022-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Native American Heritage Day</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Friday after Thanksgiving</t>
+          <t>Juneteenth</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2023-24</t>
+          <t>2022-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>Independence Day</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2023-24</t>
+          <t>2022-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Year's Day</t>
+          <t>Labor Day</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Super Bowl Eve</t>
+          <t>Veterans Day (observed)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Saturday; no-op for day typing</t>
+          <t>federal observed day</t>
         </is>
       </c>
     </row>
@@ -657,17 +657,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Saturday</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>no-op for day typing</t>
+          <t>Veterans Day</t>
         </is>
       </c>
     </row>
@@ -679,17 +674,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Sunday</t>
+          <t>Thanksgiving Day</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>no-op for day typing</t>
+          <t>4th Thursday of November</t>
         </is>
       </c>
     </row>
@@ -701,12 +696,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Memorial Day</t>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
         </is>
       </c>
     </row>
@@ -718,17 +718,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Father's Day</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Sunday; no-op for day typing</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
@@ -740,12 +735,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Independence Day</t>
+          <t>New Year's Day</t>
         </is>
       </c>
     </row>
@@ -757,151 +752,151 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Labor Day</t>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Native American Heritage Day</t>
+          <t>Memorial Day weekend - Saturday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Friday after Thanksgiving</t>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New Year's Day</t>
+          <t>Memorial Day</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Super Bowl Eve</t>
+          <t>Father's Day</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Saturday; no-op for day typing</t>
+          <t>Sunday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Saturday</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>no-op for day typing</t>
+          <t>Juneteenth</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Sunday</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>no-op for day typing</t>
+          <t>Independence Day</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2023-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Memorial Day</t>
+          <t>Labor Day</t>
         </is>
       </c>
     </row>
@@ -913,17 +908,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Father's Day</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sunday; no-op for day typing</t>
+          <t>Veterans Day</t>
         </is>
       </c>
     </row>
@@ -935,12 +925,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Independence Day</t>
+          <t>Thanksgiving Day</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4th Thursday of November</t>
         </is>
       </c>
     </row>
@@ -952,107 +947,112 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Labor Day</t>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Native American Heritage Day</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Friday after Thanksgiving</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>New Year's Day</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New Year's Day</t>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Super Bowl Eve</t>
+          <t>Memorial Day weekend - Saturday</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Saturday; no-op for day typing</t>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Saturday</t>
+          <t>Memorial Day weekend - Sunday</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1064,100 +1064,90 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Sunday</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>no-op for day typing</t>
+          <t>Memorial Day</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Memorial Day</t>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Father's Day</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Sunday; no-op for day typing</t>
+          <t>Juneteenth</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Independence Day (observed)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>federal observed day</t>
+          <t>Independence Day</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2024-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Independence Day</t>
+          <t>Labor Day</t>
         </is>
       </c>
     </row>
@@ -1169,129 +1159,129 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Labor Day</t>
+          <t>Veterans Day</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Native American Heritage Day</t>
+          <t>Thanksgiving Day</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Friday after Thanksgiving</t>
+          <t>4th Thursday of November</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New Year's Eve</t>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New Year's Day</t>
+          <t>New Year's Eve</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2027-02-13</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Super Bowl Eve</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Saturday; no-op for day typing</t>
+          <t>New Year's Day</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2027-05-29</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Saturday</t>
+          <t>Super Bowl Eve</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>no-op for day typing</t>
+          <t>Saturday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2027-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Memorial Day weekend - Sunday</t>
+          <t>Memorial Day weekend - Saturday</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1303,93 +1293,427 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2027-05-31</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memorial Day</t>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2027-06-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Father's Day</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Sunday; no-op for day typing</t>
+          <t>Memorial Day</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2027-07-04</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Independence Day</t>
+          <t>Juneteenth</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2025-26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2027-07-05</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Independence Day (observed)</t>
+          <t>Father's Day</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>federal observed day</t>
+          <t>Sunday; no-op for day typing</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Independence Day (observed)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>federal observed day</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Labor Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-11-11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Veterans Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Thanksgiving Day</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4th Thursday of November</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Native American Heritage Day</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Friday after Thanksgiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New Year's Eve</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New Year's Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2027-02-13</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Super Bowl Eve</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Saturday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2027-05-29</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Saturday</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2027-05-30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend - Sunday</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2027-05-31</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Memorial Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2027-06-18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Juneteenth (observed)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>federal observed day</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2027-06-19</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Juneteenth</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2027-06-20</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Father's Day</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sunday; no-op for day typing</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2027-07-04</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Independence Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Independence Day (observed)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>federal observed day</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>2027-09-06</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Labor Day</t>
         </is>
